--- a/literature_analysis/outputs/screening_results_snowball.xlsx
+++ b/literature_analysis/outputs/screening_results_snowball.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xp2239\Desktop\Research_RoadRestoration\literature_analysis\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237759CB-0238-4809-8D2C-D7674CBD91CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AC816B-EF7B-4C40-BC0E-E5004E0312D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12885,6 +12885,9 @@
   <sheetPr filterMode="1"/>
   <dimension ref="A1:W1218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -67235,16 +67238,9 @@
         <filter val="TRUE"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="12">
+    <filterColumn colId="15">
       <filters>
-        <filter val="network-flow/capacity"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="reinforcement-learning/DRL"/>
-        <filter val="reinforcement-learning/DRL; graph-neural-network/GNN"/>
-        <filter val="reinforcement-learning/DRL; heuristic/metaheuristic/GA"/>
+        <filter val="dynamic/time-varying-demand"/>
       </filters>
     </filterColumn>
   </autoFilter>
